--- a/TSOoficios/export_folios.xlsx
+++ b/TSOoficios/export_folios.xlsx
@@ -1,139 +1,235 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:workbookPr codeName="ThisWorkbook"/>
-  <x:bookViews>
-    <x:workbookView firstSheet="0" activeTab="0"/>
-  </x:bookViews>
-  <x:sheets>
-    <x:sheet name="Folios" sheetId="1" r:id="rId2"/>
-  </x:sheets>
-  <x:definedNames/>
-  <x:calcPr calcId="125725"/>
-</x:workbook>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moral\Desktop\TSOPIA\TSOoficios\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A96488D-8277-4D95-B4BA-BAD1209AC631}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
+  <sheets>
+    <sheet name="Folios" sheetId="1" r:id="rId1"/>
+  </sheets>
+  <calcPr calcId="0"/>
+</workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:si>
-    <x:t>oficio</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nombre</x:t>
-  </x:si>
-  <x:si>
-    <x:t>direccion</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zona</x:t>
-  </x:si>
-  <x:si>
-    <x:t>hora_apertura</x:t>
-  </x:si>
-  <x:si>
-    <x:t>hora_cierre</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tiempo_estimado_entrega</x:t>
-  </x:si>
-  <x:si>
-    <x:t>prioridad</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fecha_folio</x:t>
-  </x:si>
-  <x:si>
-    <x:t>entregado</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Centro de Salud con Servicios Ampliados</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Col.Lucio Blanco C.P 66218</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sur</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08:00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20:00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>00:30:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Baja</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10/07/2025 0:00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>False</x:t>
-  </x:si>
-</x:sst>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="53">
+  <si>
+    <t>oficio</t>
+  </si>
+  <si>
+    <t>nombre</t>
+  </si>
+  <si>
+    <t>direccion</t>
+  </si>
+  <si>
+    <t>zona</t>
+  </si>
+  <si>
+    <t>hora_apertura</t>
+  </si>
+  <si>
+    <t>hora_cierre</t>
+  </si>
+  <si>
+    <t>tiempo_estimado_entrega</t>
+  </si>
+  <si>
+    <t>prioridad</t>
+  </si>
+  <si>
+    <t>fecha_folio</t>
+  </si>
+  <si>
+    <t>entregado</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Oficina ejecutiva del gobierno del estado</t>
+  </si>
+  <si>
+    <t>Zaragoza y 5 de Mayo, Col.Centro, C.P. 64000</t>
+  </si>
+  <si>
+    <t>Centro</t>
+  </si>
+  <si>
+    <t>08:00:00</t>
+  </si>
+  <si>
+    <t>17:00:00</t>
+  </si>
+  <si>
+    <t>00:20:00</t>
+  </si>
+  <si>
+    <t>Alta</t>
+  </si>
+  <si>
+    <t>10/07/2025 0:00:00</t>
+  </si>
+  <si>
+    <t>False</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Auditoria superior del estado</t>
+  </si>
+  <si>
+    <t>Loma Larga 2550 Pte, Obispado, C.P. 64060</t>
+  </si>
+  <si>
+    <t>Poniente</t>
+  </si>
+  <si>
+    <t>16:00:00</t>
+  </si>
+  <si>
+    <t>00:45:00</t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Baja</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>PROFECO</t>
+  </si>
+  <si>
+    <t>Hidalgo 600. Centro, C.P. 64000</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>Presidencia Municipal</t>
+  </si>
+  <si>
+    <t>Av. Juárez 100, Centro, C.P. 64000</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>Secretaría de Seguridad Ciudadana (C4)</t>
+  </si>
+  <si>
+    <t>Avenida Las Torres 401, Col. Parque Industrial , C.P. 64520</t>
+  </si>
+  <si>
+    <t>Norte</t>
+  </si>
+  <si>
+    <t>00:30:00</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>IMPLAN</t>
+  </si>
+  <si>
+    <t>Palacio de Justicia, Primer Piso, Centro, C.P. 64000</t>
+  </si>
+  <si>
+    <t>Sur</t>
+  </si>
+  <si>
+    <t>00:40:00</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>Centro de Salud con Servicios Ampliados</t>
+  </si>
+  <si>
+    <t>Col.Lucio Blanco C.P 66218</t>
+  </si>
+  <si>
+    <t>20:00:00</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
-    <x:numFmt numFmtId="0" formatCode=""/>
-  </x:numFmts>
-  <x:fonts count="1">
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="11"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-  </x:fonts>
-  <x:fills count="2">
-    <x:fill>
-      <x:patternFill patternType="none"/>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="gray125"/>
-    </x:fill>
-  </x:fills>
-  <x:borders count="1">
-    <x:border diagonalUp="0" diagonalDown="0">
-      <x:left style="none">
-        <x:color rgb="FF000000"/>
-      </x:left>
-      <x:right style="none">
-        <x:color rgb="FF000000"/>
-      </x:right>
-      <x:top style="none">
-        <x:color rgb="FF000000"/>
-      </x:top>
-      <x:bottom style="none">
-        <x:color rgb="FF000000"/>
-      </x:bottom>
-      <x:diagonal style="none">
-        <x:color rgb="FF000000"/>
-      </x:diagonal>
-    </x:border>
-  </x:borders>
-  <x:cellStyleXfs count="1">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-  </x:cellStyleXfs>
-  <x:cellXfs count="1">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-  </x:cellXfs>
-  <x:cellStyles count="1">
-    <x:cellStyle name="Normal" xfId="0" builtinId="0"/>
-  </x:cellStyles>
-</x:styleSheet>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+  </fonts>
+  <fills count="2">
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+  </fills>
+  <borders count="1">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+  </borders>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0"/>
+  </cellStyleXfs>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
+</styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -420,82 +516,431 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
-  <x:dimension ref="A1:J2"/>
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:sheetData>
-    <x:row r="1" spans="1:10">
-      <x:c r="A1" s="0" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B1" s="0" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C1" s="0" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D1" s="0" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E1" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F1" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G1" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H1" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I1" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J1" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:10">
-      <x:c r="A2" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B2" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C2" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D2" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E2" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F2" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G2" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="H2" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I2" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="J2" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J13"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="3" max="3" width="43.54296875" customWidth="1"/>
+    <col min="7" max="7" width="15.54296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" t="s">
+        <v>26</v>
+      </c>
+      <c r="I7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8" t="s">
+        <v>40</v>
+      </c>
+      <c r="H8" t="s">
+        <v>26</v>
+      </c>
+      <c r="I8" t="s">
+        <v>18</v>
+      </c>
+      <c r="J8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I9" t="s">
+        <v>18</v>
+      </c>
+      <c r="J9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" t="s">
+        <v>45</v>
+      </c>
+      <c r="E10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" t="s">
+        <v>24</v>
+      </c>
+      <c r="G10" t="s">
+        <v>46</v>
+      </c>
+      <c r="H10" t="s">
+        <v>17</v>
+      </c>
+      <c r="I10" t="s">
+        <v>18</v>
+      </c>
+      <c r="J10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" t="s">
+        <v>16</v>
+      </c>
+      <c r="H11" t="s">
+        <v>26</v>
+      </c>
+      <c r="I11" t="s">
+        <v>18</v>
+      </c>
+      <c r="J11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12" t="s">
+        <v>49</v>
+      </c>
+      <c r="C12" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" t="s">
+        <v>45</v>
+      </c>
+      <c r="E12" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" t="s">
+        <v>51</v>
+      </c>
+      <c r="G12" t="s">
+        <v>46</v>
+      </c>
+      <c r="H12" t="s">
+        <v>26</v>
+      </c>
+      <c r="I12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J12" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>52</v>
+      </c>
+      <c r="B13" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" t="s">
+        <v>50</v>
+      </c>
+      <c r="D13" t="s">
+        <v>45</v>
+      </c>
+      <c r="E13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" t="s">
+        <v>51</v>
+      </c>
+      <c r="G13" t="s">
+        <v>46</v>
+      </c>
+      <c r="H13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J13" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+</worksheet>
 </file>
--- a/TSOoficios/export_folios.xlsx
+++ b/TSOoficios/export_folios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moral\Desktop\TSOPIA\TSOoficios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A96488D-8277-4D95-B4BA-BAD1209AC631}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{914B9CC0-2720-4D90-B7F6-2B0136805412}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
